--- a/mapping/Protozoa.xlsx
+++ b/mapping/Protozoa.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>贝诺孢子虫属</t>
+          <t>贝斯诺虫属</t>
         </is>
       </c>
     </row>
